--- a/04_arquitectura/entrega_2/tablas/arquitectura_fisica_Seguridad.xlsx
+++ b/04_arquitectura/entrega_2/tablas/arquitectura_fisica_Seguridad.xlsx
@@ -1,32 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Principios rectores" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.1 Los siete principios de NIS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Capa expuesta (Art. 21.2 · R" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.1 Superficie de exposición co" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.1 Modelo de identidad (Modelo" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.3 Autorización- RBAC más ABAC" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.4 Política de sesión (Art. 22" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.6 Gestión de dispositivos (MD" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.1 En tránsito" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.2 En reposo" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.3 Cifrado a nivel de campo (R" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Clasificación de la informac" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Detección, respuesta y evide" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. Modelado de amenazas STRIDE " sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. Seguridad del ciclo de desar" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Datos personales, residenci" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.5 Base de licitud por tratam" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. Matriz de controles ISO-IEC" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. Referencias cruzadas con la" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14. Trazabilidad normativa (res" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="1. Principios rectores" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2.1 Los siete principios de NIS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3. Capa expuesta (Art. 21.2 · R" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3.1 Superficie de exposición co" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4.1 Modelo de identidad (Modelo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="4.3 Autorización- RBAC más ABAC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="4.4 Política de sesión (Art. 22" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="4.6 Gestión de dispositivos (MD" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="5.1 En tránsito" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="5.2 En reposo" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="5.3 Cifrado a nivel de campo (R" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="6. Clasificación de la informac" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="7. Detección, respuesta y evide" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="10. Datos personales, residenci" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="10.5 Base de licitud por tratam" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="13. Referencias cruzadas con la" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="14. Trazabilidad normativa (res" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1188,362 +1185,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="41.65" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="46.75" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>8. Modelado de amenazas STRIDE (Art. 21.1 · RT-11.02)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Componente o integración</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Amenazas STRIDE relevantes</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Mitigación diseñada</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Verificación</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Apps de terreno (Kotlin, sin conexión)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Suplantación de usuario o dispositivo · alteración de datos locales · repudio de operaciones · denegación por buffer sin control</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>PIN o biometría más MDM (§4.6); cifrado local y buffer de escrituras inmutable; buffer acotado con monitoreo</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Pruebas de seguridad de aplicación y revisión semestral</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Puerta de enlace (API Gateway)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Suplantación de llamadas · denegación de servicio</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>OIDC con PKCE, límites de tasa, WAF y CDN en el borde, limitación exponencial</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Pruebas de carga y abuso en marcha blanca</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>API de negocio (Django, M1–M12)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Suplantación · alteración · divulgación · elevación de privilegios</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>OAuth 2.1 y mTLS, ORM con validación de entrada, RBAC más ABAC, cifrado de datos sensibles</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>SAST y DAST en el pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Colas y eventos (RabbitMQ, SQS, EventBridge)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Alteración de mensajes · repudio</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>mTLS, firma de eventos, bitácora de reconciliación (Art. 16.4)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Pruebas de contrato y auditoría</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Bases de datos (PostgreSQL, Aurora, Redshift, S3)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Divulgación · alteración</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>KMS y cifrado en reposo, política de retención y eliminación, auditoría de acceso (RT-16.09)</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Control de accesos y revisión de cifrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>ERP 2017, SII, Transbank, EDI/AS2</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Suplantación · alteración de datos intercambiados · repudio de transacciones</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>mTLS con certificados gestionados, capa anticorrupción, firmas y sumas de verificación en mensajes y exportaciones</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Pruebas de falla por integración</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Telemetría e IoT (Greengrass → DynamoDB)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Suplantación de sensores · alteración de lecturas</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Certificado X.509 por dispositivo, borde autenticado, series inmutables</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Rol de dispositivo y revisión periódica</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Portales de la DMZ (N-01, N-02, N-03)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Suplantación de cliente externo · abuso automatizado · divulgación entre entidades</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>OIDC por rol, MFA y OTP, WAF con reglas propias, protección de bots, aislamiento estricto por entidad</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Pentest previo a producción</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Sala técnica y acceso físico</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Acceso físico no autorizado · sustracción de medios</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Cuatro capas de acceso, biometría facial, esclusa con antipassback, CCTV ≥ 30 días, custodia de medios</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Auditoría física y bitácora</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28.05" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>9. Seguridad del ciclo de desarrollo (Art. 21.4 · RT-11.22 a RT-11.27)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Análisis en el pipeline</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>SAST, análisis de composición de software, DAST y escaneo de imágenes de contenedor, con bloqueo automático del despliegue ante hallazgos críticos o altos</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>SBOM por versión</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Inventario de componentes en CycloneDX, generado en el pipeline y entregado al CLIENTE junto con cada versión liberada</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Firma de artefactos y procedencia</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Imágenes OCI y SBOM firmados con Sigstore/cosign; construcción hermética con procedencia SLSA nivel 3, verificada antes de cada despliegue</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Secretos</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Prohibición absoluta de credenciales embebidas; gestor de secretos con rotación automática (§5.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Datos no productivos</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Desarrollo, calidad y preproducción operan con datos sintéticos derivados de la volumetría del Cap. 14; las plantillas cercanas a producción pasan por anonimización o seudonimización verificable</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Acceso a producción</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Sin acceso interactivo: los despliegues son exclusivamente por pipeline; la excepción es just-in-time con MFA, aprobación y grabación de sesión</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1719,7 +1360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1922,356 +1563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="47.6" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>11. Matriz de controles ISO/IEC 27001:2022 (RT-11.05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Control (Anexo A)</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Aplicación en Puelche</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Evidencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>5.7 Inteligencia de amenazas</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Casos de uso del SIEM alimentados con contexto del sector logístico</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Catálogo de detecciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>5.15 Control de acceso</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>RBAC más ABAC sobre los 11 actores canónicos (§4.3)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Políticas de Keycloak y de la Capa 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>5.16 Gestión de acceso privilegiado</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>PAM just-in-time y break-glass (§4.8)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Procedimiento escrito y sesiones grabadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>5.17 / 5.18 Autenticación y gestión de identidades</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>OIDC, OAuth 2.1, MFA, aprovisionamiento y baja ≤ 24 h (§4.7)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Keycloak y MDM</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>5.19 / 5.20 Relaciones con proveedores</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>OTP para conductores externos, aislamiento por proveedor (§4.3)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Contratos y mecanismo OTP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>5.23 / 5.24 Seguridad en la nube y gestión de incidentes</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Multi-AZ, GuardDuty, WAF, IAM, KMS, IaC; plan de respuesta (§7)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Configuración de cuentas y plan de incidentes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>5.31 / 5.34 Cumplimiento legal y privacidad</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Ley 21.719, Ley 19.799, residencia y transferencia (§10)</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Inventario de tratamientos, protocolo ARCOP y política de privacidad (§10.1–10.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>6.8 Notificación de eventos de seguridad</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Canal declarado y plazos de 2 h y 24 h (§7)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Registro de notificaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>7.10 / 7.11 Respaldo y capacidad</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Aurora con PITR de 35 días, WAL on-premise, CDC; RPO 15 min y RTO 4 h</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Simulacro semestral (Art. 20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>7.12 / 8.8 Redes y vulnerabilidades</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Microsegmentación con mTLS, parches por Ansible, escaneo semanal (§7)</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Plan de parches e informes de escaneo</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>8.5 Autenticación segura</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>MFA, FIDO2 para administradores, PIN más posesión en terreno (§4.2, §4.5)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Configuración del IdP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>8.10 Eliminación de la información</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Retención y eliminación certificada por categoría (§10)</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Registro inalterable</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>8.11 Enmascaramiento de datos</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Cifrado a nivel de campo de geolocalización y antecedentes comerciales (§5.3)</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Inventario de campos cifrados</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>8.15 / 8.16 Registro, monitoreo y SIEM</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Registros inalterables y alertas por síntomas de negocio (§7)</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Capa 8 y correlación por transaction_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>8.17 Sincronización de relojes</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>NTP en borde, on-premise y nube</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Configuración y verificación</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>8.23 Auditoría de registros</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Revisión periódica por el Encargado de Seguridad (RT-16.09)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Procedimiento de auditoría</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>8.25 / 8.28 Desarrollo seguro y codificación segura</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>SAST, DAST, SCA, SBOM, SLSA 3 (§9)</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Pipeline y repositorio</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>8.31 Separación de ambientes</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Cinco cuentas AWS aisladas con SCP (RT-04.01)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Organización de cuentas</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2396,6 +1688,331 @@
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Gestión de secretos en servicio administrado (SEC-01, §5.3) — adoptada y propagada el 2026-09-06</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45.05" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>14. Trazabilidad normativa (resumen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Requisito</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Cómo se cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>BA Art. 21.1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Zero Trust NIST SP 800-207 (§2); STRIDE por componente e integración (§8); clasificación de la información (§6); plazos de remediación 7/15/30 días (§7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>BA Art. 21.2</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Capa expuesta con CDN, WAF y Shield; TLS 1.3 con HSTS; cifrado en reposo con KMS y separación de funciones; puerta de enlace con cuotas, esquema y carga útil; protección de bots (§3, §5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>BA Art. 21.3</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Registro centralizado e inalterable con 12 + 24 meses; SIEM con casos de uso del negocio; EDR en ambos dominios; respuesta en 2 h; brechas en 24 h; pentest anual y previo a producción (§7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>BA Art. 21.4</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>SAST, DAST, SCA y escaneo de imágenes con bloqueo; SBOM CycloneDX; SLSA 3; sin secretos embebidos; sin datos productivos en ambientes no productivos (§9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>BA Art. 22</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Identidad centralizada con OIDC/OAuth 2.1 y LDAP; SSO con cierre propagado; MFA; FIDO2; RBAC y ABAC con segregación de funciones; PAM; política de sesión completa; auditoría de identidad; baja ≤ 24 h; perfil operacional de terreno (§4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>BA Art. 23</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Residencia declarada, transferencia internacional con base de licitud y resguardos, retención por categoría, eliminación segura y exportabilidad (§10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>RT-11.02</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Modelado STRIDE por componente e integración (§8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>RT-11.03</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Clasificación en cuatro niveles con controles diferenciados (§6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>RT-11.04</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Programa de vulnerabilidades con plazos y verificación de corrección (§7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>RT-11.05</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Matriz de controles ISO/IEC 27001:2022 (§11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>RT-11.08 / RT-11.09</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>TLS 1.3 con gestión de certificados; cifrado en reposo con KMS y rotación (§5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>RT-11.10</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Cifrado a nivel de campo para los cuatro conjuntos que fija el Cap. 15 del caso (§5.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>RT-11.11</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Puerta de enlace con autenticación, cuotas, límites, esquema e inspección de carga útil (§3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>RT-11.13</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Superficie de exposición completa por zona y sitio (§3.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>RT-11.14 / RT-11.15 / RT-11.17</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Eventos inalterables con retención; SIEM; SOC 24×7 (§7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>RT-11.18 / RT-11.19 / RT-11.20 / RT-11.21</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Plan de respuesta, notificación de brechas, pentest independiente y simulacros con el CLIENTE (§7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>RT-11.22 a RT-11.27</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Seguridad del ciclo de desarrollo (§9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>RT-12.01 a RT-12.13</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Identidad, acceso y sesiones completos (§4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>RT-03.15</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Endurecimiento CIS con gestión centralizada de parches (§7, F-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>RT-03.18</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>MDM de dispositivos de borde y terreno (§4.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>RT-03.22</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Acceso remoto con confianza cero y verificación de postura; sin servicios internos expuestos (§2.2, §3.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>RT-16.07 / RT-16.09</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Registro inalterable y registro de consultas a información sensible (§5.3, §7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Caso Cap. 15 (RT-11.10, RT-12.11, RT-12.12, RT-16.09)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Cifrado a nivel de campo (§5.3); autenticación con guantes, a una mano y en dispositivos compartidos (§4.5); usuarios externos (§4.2, §4.3); registro de consultas (§5.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Caso Cap. 17.4, puntos 3 y 9</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Operación de un turno completo sin señal con autenticación local (§4.1, §4.5); incorporación de conductores de terceros con OTP y sin cuenta corporativa (§4.2)</t>
         </is>
       </c>
     </row>
@@ -2517,331 +2134,6 @@
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>SIEM (Security Lake) con casos de uso del proceso logístico, no solo de infraestructura; correlación por transaction_id en la Capa 8</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45.05" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>14. Trazabilidad normativa (resumen)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Requisito</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Cómo se cumple</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>BA Art. 21.1</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Zero Trust NIST SP 800-207 (§2); STRIDE por componente e integración (§8); clasificación de la información (§6); plazos de remediación 7/15/30 días (§7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>BA Art. 21.2</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Capa expuesta con CDN, WAF y Shield; TLS 1.3 con HSTS; cifrado en reposo con KMS y separación de funciones; puerta de enlace con cuotas, esquema y carga útil; protección de bots (§3, §5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>BA Art. 21.3</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Registro centralizado e inalterable con 12 + 24 meses; SIEM con casos de uso del negocio; EDR en ambos dominios; respuesta en 2 h; brechas en 24 h; pentest anual y previo a producción (§7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>BA Art. 21.4</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>SAST, DAST, SCA y escaneo de imágenes con bloqueo; SBOM CycloneDX; SLSA 3; sin secretos embebidos; sin datos productivos en ambientes no productivos (§9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>BA Art. 22</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Identidad centralizada con OIDC/OAuth 2.1 y LDAP; SSO con cierre propagado; MFA; FIDO2; RBAC y ABAC con segregación de funciones; PAM; política de sesión completa; auditoría de identidad; baja ≤ 24 h; perfil operacional de terreno (§4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>BA Art. 23</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Residencia declarada, transferencia internacional con base de licitud y resguardos, retención por categoría, eliminación segura y exportabilidad (§10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>RT-11.02</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Modelado STRIDE por componente e integración (§8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>RT-11.03</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Clasificación en cuatro niveles con controles diferenciados (§6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>RT-11.04</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Programa de vulnerabilidades con plazos y verificación de corrección (§7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>RT-11.05</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Matriz de controles ISO/IEC 27001:2022 (§11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>RT-11.08 / RT-11.09</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>TLS 1.3 con gestión de certificados; cifrado en reposo con KMS y rotación (§5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>RT-11.10</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Cifrado a nivel de campo para los cuatro conjuntos que fija el Cap. 15 del caso (§5.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>RT-11.11</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Puerta de enlace con autenticación, cuotas, límites, esquema e inspección de carga útil (§3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>RT-11.13</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Superficie de exposición completa por zona y sitio (§3.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>RT-11.14 / RT-11.15 / RT-11.17</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Eventos inalterables con retención; SIEM; SOC 24×7 (§7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>RT-11.18 / RT-11.19 / RT-11.20 / RT-11.21</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Plan de respuesta, notificación de brechas, pentest independiente y simulacros con el CLIENTE (§7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>RT-11.22 a RT-11.27</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Seguridad del ciclo de desarrollo (§9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>RT-12.01 a RT-12.13</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Identidad, acceso y sesiones completos (§4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>RT-03.15</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Endurecimiento CIS con gestión centralizada de parches (§7, F-02)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>RT-03.18</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>MDM de dispositivos de borde y terreno (§4.6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>RT-03.22</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Acceso remoto con confianza cero y verificación de postura; sin servicios internos expuestos (§2.2, §3.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>RT-16.07 / RT-16.09</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Registro inalterable y registro de consultas a información sensible (§5.3, §7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Caso Cap. 15 (RT-11.10, RT-12.11, RT-12.12, RT-16.09)</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Cifrado a nivel de campo (§5.3); autenticación con guantes, a una mano y en dispositivos compartidos (§4.5); usuarios externos (§4.2, §4.3); registro de consultas (§5.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Caso Cap. 17.4, puntos 3 y 9</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Operación de un turno completo sin señal con autenticación local (§4.1, §4.5); incorporación de conductores de terceros con OTP y sin cuenta corporativa (§4.2)</t>
         </is>
       </c>
     </row>

--- a/04_arquitectura/entrega_2/tablas/arquitectura_fisica_Seguridad.xlsx
+++ b/04_arquitectura/entrega_2/tablas/arquitectura_fisica_Seguridad.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Todo tráfico on-premise → nube es saliente. Las dos únicas excepciones (DMS → PostgreSQL y celery-erp-sync → ACL) están declaradas, acotadas al túnel IPsec autenticado y auditadas.</t>
+          <t>Todo tráfico on-premise → nube es saliente. Las dos únicas excepciones (DMS → PostgreSQL y erp-sync → ACL) están declaradas, acotadas al túnel IPsec autenticado y auditadas.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Solo lectura, TTL 8 h</t>
+          <t>Solo lectura, TTL 24 h (no emite sesiones)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Solo lectura, TTL 8 h</t>
+          <t>Solo lectura, TTL 24 h (no emite sesiones)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>TTL 8 h (turno nocturno de preparación, RNF-13.01)</t>
+          <t>Credencial de turno de 8 h (turno nocturno de preparación, RNF-13.01); relevos sin enlace por el verificador local</t>
         </is>
       </c>
     </row>
